--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="232">
   <si>
     <t>Id</t>
   </si>
@@ -713,9 +713,6 @@
   </si>
   <si>
     <t>虚无权杖</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>虚无战锤</t>
@@ -1696,7 +1693,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K202"/>
+  <dimension ref="C3:K202"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -7217,7 +7214,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="193" customHeight="1" spans="1:11">
+    <row r="193" customHeight="1" spans="3:11">
       <c r="C193" s="1">
         <v>40000238</v>
       </c>
@@ -7246,7 +7243,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="194" customHeight="1" spans="1:11">
+    <row r="194" customHeight="1" spans="3:11">
       <c r="C194" s="1">
         <v>40000239</v>
       </c>
@@ -7275,13 +7272,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" customHeight="1" spans="1:11">
-      <c r="A195" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>227</v>
-      </c>
+    <row r="195" customHeight="1" spans="3:11">
       <c r="C195" s="1">
         <v>40000240</v>
       </c>
@@ -7292,7 +7283,7 @@
         <v>6</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G195" s="2">
         <v>2001</v>
@@ -7310,13 +7301,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="196" customHeight="1" spans="1:11">
-      <c r="A196" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>227</v>
-      </c>
+    <row r="196" customHeight="1" spans="3:11">
       <c r="C196" s="1">
         <v>40000241</v>
       </c>
@@ -7327,7 +7312,7 @@
         <v>6</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G196" s="4">
         <v>2004</v>
@@ -7345,13 +7330,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="197" customHeight="1" spans="1:11">
-      <c r="A197" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>227</v>
-      </c>
+    <row r="197" customHeight="1" spans="3:11">
       <c r="C197" s="1">
         <v>40000242</v>
       </c>
@@ -7362,7 +7341,7 @@
         <v>6</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G197" s="1">
         <v>2005</v>
@@ -7380,13 +7359,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="198" customHeight="1" spans="1:11">
-      <c r="A198" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>227</v>
-      </c>
+    <row r="198" customHeight="1" spans="3:11">
       <c r="C198" s="1">
         <v>40000243</v>
       </c>
@@ -7397,7 +7370,7 @@
         <v>6</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G198" s="1">
         <v>2006</v>
@@ -7415,13 +7388,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="199" customHeight="1" spans="1:11">
-      <c r="A199" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>227</v>
-      </c>
+    <row r="199" customHeight="1" spans="3:11">
       <c r="C199" s="1">
         <v>40000244</v>
       </c>
@@ -7432,7 +7399,7 @@
         <v>6</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G199" s="1">
         <v>2010</v>
@@ -7450,15 +7417,15 @@
         <v>92</v>
       </c>
     </row>
-    <row r="200" customHeight="1" spans="1:11">
+    <row r="200" customHeight="1" spans="3:11">
       <c r="H200" s="4"/>
       <c r="I200" s="4"/>
     </row>
-    <row r="201" customHeight="1" spans="1:11">
+    <row r="201" customHeight="1" spans="3:11">
       <c r="H201" s="4"/>
       <c r="I201" s="4"/>
     </row>
-    <row r="202" customHeight="1" spans="1:11">
+    <row r="202" customHeight="1" spans="3:11">
       <c r="H202" s="4"/>
       <c r="I202" s="4"/>
     </row>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="267">
   <si>
     <t>Id</t>
   </si>
@@ -728,6 +728,111 @@
   </si>
   <si>
     <t>虚无龙爪</t>
+  </si>
+  <si>
+    <t>鸿蒙鸡爪</t>
+  </si>
+  <si>
+    <t>鸿蒙鹿茸</t>
+  </si>
+  <si>
+    <t>鸿蒙草帽</t>
+  </si>
+  <si>
+    <t>鸿蒙猫爪</t>
+  </si>
+  <si>
+    <t>鸿蒙花朵</t>
+  </si>
+  <si>
+    <t>鸿蒙冰晶</t>
+  </si>
+  <si>
+    <t>鸿蒙蝠翼</t>
+  </si>
+  <si>
+    <t>鸿蒙魂火</t>
+  </si>
+  <si>
+    <t>鸿蒙腐肉</t>
+  </si>
+  <si>
+    <t>鸿蒙蛇胆</t>
+  </si>
+  <si>
+    <t>鸿蒙狼爪</t>
+  </si>
+  <si>
+    <t>鸿蒙虫皮</t>
+  </si>
+  <si>
+    <t>鸿蒙鹰羽</t>
+  </si>
+  <si>
+    <t>鸿蒙虫角</t>
+  </si>
+  <si>
+    <t>鸿蒙蜈膏</t>
+  </si>
+  <si>
+    <t>鸿蒙虫心</t>
+  </si>
+  <si>
+    <t>鸿蒙龙皮</t>
+  </si>
+  <si>
+    <t>鸿蒙猪皮</t>
+  </si>
+  <si>
+    <t>鸿蒙猪心</t>
+  </si>
+  <si>
+    <t>鸿蒙蝎皮</t>
+  </si>
+  <si>
+    <t>鸿蒙宝甲</t>
+  </si>
+  <si>
+    <t>鸿蒙号角</t>
+  </si>
+  <si>
+    <t>鸿蒙雕像</t>
+  </si>
+  <si>
+    <t>鸿蒙神像</t>
+  </si>
+  <si>
+    <t>鸿蒙獠牙</t>
+  </si>
+  <si>
+    <t>鸿蒙树心</t>
+  </si>
+  <si>
+    <t>鸿蒙魔心</t>
+  </si>
+  <si>
+    <t>鸿蒙尸心</t>
+  </si>
+  <si>
+    <t>鸿蒙法杖</t>
+  </si>
+  <si>
+    <t>鸿蒙权杖</t>
+  </si>
+  <si>
+    <t>鸿蒙战锤</t>
+  </si>
+  <si>
+    <t>鸿蒙血核</t>
+  </si>
+  <si>
+    <t>鸿蒙魔核</t>
+  </si>
+  <si>
+    <t>鸿蒙龙甲</t>
+  </si>
+  <si>
+    <t>鸿蒙龙爪</t>
   </si>
 </sst>
 </file>
@@ -1693,7 +1798,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:K202"/>
+  <dimension ref="C3:K236"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -7418,16 +7523,1025 @@
       </c>
     </row>
     <row r="200" customHeight="1" spans="3:11">
-      <c r="H200" s="4"/>
-      <c r="I200" s="4"/>
+      <c r="C200" s="1">
+        <v>40000245</v>
+      </c>
+      <c r="D200" s="1">
+        <v>40000245</v>
+      </c>
+      <c r="E200" s="2">
+        <v>7</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G200" s="2">
+        <v>2001</v>
+      </c>
+      <c r="H200" s="2">
+        <v>12</v>
+      </c>
+      <c r="I200" s="2">
+        <v>12</v>
+      </c>
+      <c r="J200" s="2">
+        <v>4</v>
+      </c>
+      <c r="K200" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="201" customHeight="1" spans="3:11">
-      <c r="H201" s="4"/>
-      <c r="I201" s="4"/>
+      <c r="C201" s="1">
+        <v>40000246</v>
+      </c>
+      <c r="D201" s="1">
+        <v>40000246</v>
+      </c>
+      <c r="E201" s="1">
+        <v>7</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G201" s="4">
+        <v>2004</v>
+      </c>
+      <c r="H201" s="4">
+        <v>12</v>
+      </c>
+      <c r="I201" s="4">
+        <v>12</v>
+      </c>
+      <c r="J201" s="4">
+        <v>4</v>
+      </c>
+      <c r="K201" s="4" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="202" customHeight="1" spans="3:11">
-      <c r="H202" s="4"/>
-      <c r="I202" s="4"/>
+      <c r="C202" s="1">
+        <v>40000247</v>
+      </c>
+      <c r="D202" s="1">
+        <v>40000247</v>
+      </c>
+      <c r="E202" s="1">
+        <v>7</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G202" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H202" s="4">
+        <v>12</v>
+      </c>
+      <c r="I202" s="4">
+        <v>12</v>
+      </c>
+      <c r="J202" s="1">
+        <v>4</v>
+      </c>
+      <c r="K202" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" spans="3:11">
+      <c r="C203" s="1">
+        <v>40000248</v>
+      </c>
+      <c r="D203" s="1">
+        <v>40000248</v>
+      </c>
+      <c r="E203" s="1">
+        <v>7</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G203" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H203" s="4">
+        <v>12</v>
+      </c>
+      <c r="I203" s="4">
+        <v>12</v>
+      </c>
+      <c r="J203" s="1">
+        <v>4</v>
+      </c>
+      <c r="K203" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" spans="3:11">
+      <c r="C204" s="1">
+        <v>40000249</v>
+      </c>
+      <c r="D204" s="1">
+        <v>40000249</v>
+      </c>
+      <c r="E204" s="1">
+        <v>7</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G204" s="1">
+        <v>2010</v>
+      </c>
+      <c r="H204" s="4">
+        <v>12</v>
+      </c>
+      <c r="I204" s="4">
+        <v>12</v>
+      </c>
+      <c r="J204" s="1">
+        <v>4</v>
+      </c>
+      <c r="K204" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" spans="3:11">
+      <c r="C205" s="1">
+        <v>40000250</v>
+      </c>
+      <c r="D205" s="1">
+        <v>40000250</v>
+      </c>
+      <c r="E205" s="1">
+        <v>7</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G205" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H205" s="4">
+        <v>12</v>
+      </c>
+      <c r="I205" s="4">
+        <v>12</v>
+      </c>
+      <c r="J205" s="1">
+        <v>4</v>
+      </c>
+      <c r="K205" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" spans="3:11">
+      <c r="C206" s="1">
+        <v>40000251</v>
+      </c>
+      <c r="D206" s="1">
+        <v>40000251</v>
+      </c>
+      <c r="E206" s="1">
+        <v>7</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G206" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H206" s="4">
+        <v>12</v>
+      </c>
+      <c r="I206" s="4">
+        <v>12</v>
+      </c>
+      <c r="J206" s="1">
+        <v>4</v>
+      </c>
+      <c r="K206" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" spans="3:11">
+      <c r="C207" s="1">
+        <v>40000252</v>
+      </c>
+      <c r="D207" s="1">
+        <v>40000252</v>
+      </c>
+      <c r="E207" s="1">
+        <v>7</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G207" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H207" s="4">
+        <v>12</v>
+      </c>
+      <c r="I207" s="4">
+        <v>12</v>
+      </c>
+      <c r="J207" s="1">
+        <v>4</v>
+      </c>
+      <c r="K207" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" spans="3:11">
+      <c r="C208" s="1">
+        <v>40000253</v>
+      </c>
+      <c r="D208" s="1">
+        <v>40000253</v>
+      </c>
+      <c r="E208" s="1">
+        <v>7</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G208" s="1">
+        <v>2013</v>
+      </c>
+      <c r="H208" s="1">
+        <v>24</v>
+      </c>
+      <c r="I208" s="1">
+        <v>24</v>
+      </c>
+      <c r="J208" s="1">
+        <v>4</v>
+      </c>
+      <c r="K208" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" spans="3:11">
+      <c r="C209" s="1">
+        <v>40000254</v>
+      </c>
+      <c r="D209" s="1">
+        <v>40000254</v>
+      </c>
+      <c r="E209" s="1">
+        <v>7</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G209" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H209" s="1">
+        <v>75</v>
+      </c>
+      <c r="I209" s="1">
+        <v>75</v>
+      </c>
+      <c r="J209" s="1">
+        <v>4</v>
+      </c>
+      <c r="K209" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" spans="3:11">
+      <c r="C210" s="1">
+        <v>40000255</v>
+      </c>
+      <c r="D210" s="1">
+        <v>40000255</v>
+      </c>
+      <c r="E210" s="1">
+        <v>7</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G210" s="2">
+        <v>2001</v>
+      </c>
+      <c r="H210" s="2">
+        <v>12</v>
+      </c>
+      <c r="I210" s="2">
+        <v>12</v>
+      </c>
+      <c r="J210" s="2">
+        <v>4</v>
+      </c>
+      <c r="K210" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="211" customHeight="1" spans="3:11">
+      <c r="C211" s="1">
+        <v>40000256</v>
+      </c>
+      <c r="D211" s="1">
+        <v>40000256</v>
+      </c>
+      <c r="E211" s="1">
+        <v>7</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G211" s="4">
+        <v>2004</v>
+      </c>
+      <c r="H211" s="4">
+        <v>12</v>
+      </c>
+      <c r="I211" s="4">
+        <v>12</v>
+      </c>
+      <c r="J211" s="4">
+        <v>4</v>
+      </c>
+      <c r="K211" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="212" customHeight="1" spans="3:11">
+      <c r="C212" s="1">
+        <v>40000257</v>
+      </c>
+      <c r="D212" s="1">
+        <v>40000257</v>
+      </c>
+      <c r="E212" s="1">
+        <v>7</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G212" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H212" s="4">
+        <v>12</v>
+      </c>
+      <c r="I212" s="4">
+        <v>12</v>
+      </c>
+      <c r="J212" s="1">
+        <v>4</v>
+      </c>
+      <c r="K212" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="213" customHeight="1" spans="3:11">
+      <c r="C213" s="1">
+        <v>40000258</v>
+      </c>
+      <c r="D213" s="1">
+        <v>40000258</v>
+      </c>
+      <c r="E213" s="1">
+        <v>7</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G213" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H213" s="4">
+        <v>12</v>
+      </c>
+      <c r="I213" s="4">
+        <v>12</v>
+      </c>
+      <c r="J213" s="1">
+        <v>4</v>
+      </c>
+      <c r="K213" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="214" customHeight="1" spans="3:11">
+      <c r="C214" s="1">
+        <v>40000259</v>
+      </c>
+      <c r="D214" s="1">
+        <v>40000259</v>
+      </c>
+      <c r="E214" s="1">
+        <v>7</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G214" s="1">
+        <v>2010</v>
+      </c>
+      <c r="H214" s="4">
+        <v>12</v>
+      </c>
+      <c r="I214" s="4">
+        <v>12</v>
+      </c>
+      <c r="J214" s="1">
+        <v>4</v>
+      </c>
+      <c r="K214" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="215" customHeight="1" spans="3:11">
+      <c r="C215" s="1">
+        <v>40000260</v>
+      </c>
+      <c r="D215" s="1">
+        <v>40000260</v>
+      </c>
+      <c r="E215" s="1">
+        <v>7</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G215" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H215" s="4">
+        <v>12</v>
+      </c>
+      <c r="I215" s="4">
+        <v>12</v>
+      </c>
+      <c r="J215" s="1">
+        <v>4</v>
+      </c>
+      <c r="K215" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="216" customHeight="1" spans="3:11">
+      <c r="C216" s="1">
+        <v>40000261</v>
+      </c>
+      <c r="D216" s="1">
+        <v>40000261</v>
+      </c>
+      <c r="E216" s="1">
+        <v>7</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G216" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H216" s="4">
+        <v>12</v>
+      </c>
+      <c r="I216" s="4">
+        <v>12</v>
+      </c>
+      <c r="J216" s="1">
+        <v>4</v>
+      </c>
+      <c r="K216" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" spans="3:11">
+      <c r="C217" s="1">
+        <v>40000262</v>
+      </c>
+      <c r="D217" s="1">
+        <v>40000262</v>
+      </c>
+      <c r="E217" s="1">
+        <v>7</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G217" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H217" s="4">
+        <v>12</v>
+      </c>
+      <c r="I217" s="4">
+        <v>12</v>
+      </c>
+      <c r="J217" s="1">
+        <v>4</v>
+      </c>
+      <c r="K217" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" spans="3:11">
+      <c r="C218" s="1">
+        <v>40000263</v>
+      </c>
+      <c r="D218" s="1">
+        <v>40000263</v>
+      </c>
+      <c r="E218" s="1">
+        <v>7</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G218" s="1">
+        <v>2013</v>
+      </c>
+      <c r="H218" s="1">
+        <v>24</v>
+      </c>
+      <c r="I218" s="1">
+        <v>24</v>
+      </c>
+      <c r="J218" s="1">
+        <v>4</v>
+      </c>
+      <c r="K218" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" spans="3:11">
+      <c r="C219" s="1">
+        <v>40000264</v>
+      </c>
+      <c r="D219" s="1">
+        <v>40000264</v>
+      </c>
+      <c r="E219" s="1">
+        <v>7</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G219" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H219" s="1">
+        <v>75</v>
+      </c>
+      <c r="I219" s="1">
+        <v>75</v>
+      </c>
+      <c r="J219" s="1">
+        <v>4</v>
+      </c>
+      <c r="K219" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" spans="3:11">
+      <c r="C220" s="1">
+        <v>40000265</v>
+      </c>
+      <c r="D220" s="1">
+        <v>40000265</v>
+      </c>
+      <c r="E220" s="1">
+        <v>7</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="G220" s="2">
+        <v>2001</v>
+      </c>
+      <c r="H220" s="2">
+        <v>12</v>
+      </c>
+      <c r="I220" s="2">
+        <v>12</v>
+      </c>
+      <c r="J220" s="2">
+        <v>4</v>
+      </c>
+      <c r="K220" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" spans="3:11">
+      <c r="C221" s="1">
+        <v>40000266</v>
+      </c>
+      <c r="D221" s="1">
+        <v>40000266</v>
+      </c>
+      <c r="E221" s="1">
+        <v>7</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G221" s="4">
+        <v>2004</v>
+      </c>
+      <c r="H221" s="4">
+        <v>12</v>
+      </c>
+      <c r="I221" s="4">
+        <v>12</v>
+      </c>
+      <c r="J221" s="4">
+        <v>4</v>
+      </c>
+      <c r="K221" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="222" customHeight="1" spans="3:11">
+      <c r="C222" s="1">
+        <v>40000267</v>
+      </c>
+      <c r="D222" s="1">
+        <v>40000267</v>
+      </c>
+      <c r="E222" s="1">
+        <v>7</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G222" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H222" s="4">
+        <v>12</v>
+      </c>
+      <c r="I222" s="4">
+        <v>12</v>
+      </c>
+      <c r="J222" s="1">
+        <v>4</v>
+      </c>
+      <c r="K222" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" spans="3:11">
+      <c r="C223" s="1">
+        <v>40000268</v>
+      </c>
+      <c r="D223" s="1">
+        <v>40000268</v>
+      </c>
+      <c r="E223" s="1">
+        <v>7</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G223" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H223" s="4">
+        <v>12</v>
+      </c>
+      <c r="I223" s="4">
+        <v>12</v>
+      </c>
+      <c r="J223" s="1">
+        <v>4</v>
+      </c>
+      <c r="K223" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="224" customHeight="1" spans="3:11">
+      <c r="C224" s="1">
+        <v>40000269</v>
+      </c>
+      <c r="D224" s="1">
+        <v>40000269</v>
+      </c>
+      <c r="E224" s="1">
+        <v>7</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G224" s="1">
+        <v>2010</v>
+      </c>
+      <c r="H224" s="4">
+        <v>12</v>
+      </c>
+      <c r="I224" s="4">
+        <v>12</v>
+      </c>
+      <c r="J224" s="1">
+        <v>4</v>
+      </c>
+      <c r="K224" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="225" customHeight="1" spans="3:11">
+      <c r="C225" s="1">
+        <v>40000270</v>
+      </c>
+      <c r="D225" s="1">
+        <v>40000270</v>
+      </c>
+      <c r="E225" s="1">
+        <v>7</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G225" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H225" s="4">
+        <v>12</v>
+      </c>
+      <c r="I225" s="4">
+        <v>12</v>
+      </c>
+      <c r="J225" s="1">
+        <v>4</v>
+      </c>
+      <c r="K225" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="226" customHeight="1" spans="3:11">
+      <c r="C226" s="1">
+        <v>40000271</v>
+      </c>
+      <c r="D226" s="1">
+        <v>40000271</v>
+      </c>
+      <c r="E226" s="1">
+        <v>7</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G226" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H226" s="4">
+        <v>12</v>
+      </c>
+      <c r="I226" s="4">
+        <v>12</v>
+      </c>
+      <c r="J226" s="1">
+        <v>4</v>
+      </c>
+      <c r="K226" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="227" customHeight="1" spans="3:11">
+      <c r="C227" s="1">
+        <v>40000272</v>
+      </c>
+      <c r="D227" s="1">
+        <v>40000272</v>
+      </c>
+      <c r="E227" s="1">
+        <v>7</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G227" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H227" s="4">
+        <v>12</v>
+      </c>
+      <c r="I227" s="4">
+        <v>12</v>
+      </c>
+      <c r="J227" s="1">
+        <v>4</v>
+      </c>
+      <c r="K227" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="228" customHeight="1" spans="3:11">
+      <c r="C228" s="1">
+        <v>40000273</v>
+      </c>
+      <c r="D228" s="1">
+        <v>40000273</v>
+      </c>
+      <c r="E228" s="1">
+        <v>7</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G228" s="1">
+        <v>2013</v>
+      </c>
+      <c r="H228" s="1">
+        <v>24</v>
+      </c>
+      <c r="I228" s="1">
+        <v>24</v>
+      </c>
+      <c r="J228" s="1">
+        <v>4</v>
+      </c>
+      <c r="K228" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" spans="3:11">
+      <c r="C229" s="1">
+        <v>40000274</v>
+      </c>
+      <c r="D229" s="1">
+        <v>40000274</v>
+      </c>
+      <c r="E229" s="1">
+        <v>7</v>
+      </c>
+      <c r="F229" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G229" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H229" s="1">
+        <v>75</v>
+      </c>
+      <c r="I229" s="1">
+        <v>75</v>
+      </c>
+      <c r="J229" s="1">
+        <v>4</v>
+      </c>
+      <c r="K229" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="230" customHeight="1" spans="3:11">
+      <c r="C230" s="1">
+        <v>40000275</v>
+      </c>
+      <c r="D230" s="1">
+        <v>40000275</v>
+      </c>
+      <c r="E230" s="1">
+        <v>7</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G230" s="2">
+        <v>2001</v>
+      </c>
+      <c r="H230" s="2">
+        <v>12</v>
+      </c>
+      <c r="I230" s="2">
+        <v>12</v>
+      </c>
+      <c r="J230" s="2">
+        <v>4</v>
+      </c>
+      <c r="K230" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="231" customHeight="1" spans="3:11">
+      <c r="C231" s="1">
+        <v>40000276</v>
+      </c>
+      <c r="D231" s="1">
+        <v>40000276</v>
+      </c>
+      <c r="E231" s="1">
+        <v>7</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G231" s="4">
+        <v>2004</v>
+      </c>
+      <c r="H231" s="4">
+        <v>12</v>
+      </c>
+      <c r="I231" s="4">
+        <v>12</v>
+      </c>
+      <c r="J231" s="4">
+        <v>4</v>
+      </c>
+      <c r="K231" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" spans="3:11">
+      <c r="C232" s="1">
+        <v>40000277</v>
+      </c>
+      <c r="D232" s="1">
+        <v>40000277</v>
+      </c>
+      <c r="E232" s="1">
+        <v>7</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G232" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H232" s="4">
+        <v>12</v>
+      </c>
+      <c r="I232" s="4">
+        <v>12</v>
+      </c>
+      <c r="J232" s="1">
+        <v>4</v>
+      </c>
+      <c r="K232" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" spans="3:11">
+      <c r="C233" s="1">
+        <v>40000278</v>
+      </c>
+      <c r="D233" s="1">
+        <v>40000278</v>
+      </c>
+      <c r="E233" s="1">
+        <v>7</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G233" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H233" s="4">
+        <v>12</v>
+      </c>
+      <c r="I233" s="4">
+        <v>12</v>
+      </c>
+      <c r="J233" s="1">
+        <v>4</v>
+      </c>
+      <c r="K233" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" spans="3:11">
+      <c r="C234" s="1">
+        <v>40000279</v>
+      </c>
+      <c r="D234" s="1">
+        <v>40000279</v>
+      </c>
+      <c r="E234" s="1">
+        <v>7</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G234" s="1">
+        <v>2010</v>
+      </c>
+      <c r="H234" s="4">
+        <v>12</v>
+      </c>
+      <c r="I234" s="4">
+        <v>12</v>
+      </c>
+      <c r="J234" s="1">
+        <v>4</v>
+      </c>
+      <c r="K234" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" spans="3:11">
+      <c r="H235" s="4"/>
+    </row>
+    <row r="236" customHeight="1" spans="3:11">
+      <c r="H236" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
